--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>12.89837857673997</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>10.55536686530605</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>12.06054340417881</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>14.88281645178333</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>11.51969815325207</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>18.83333333333333</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>15.02516175413371</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>14.00790923824959</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,9 +551,6 @@
       </c>
       <c r="E10">
         <v>7.754626358704786</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,152 +404,171 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B3">
-        <v>1074167</v>
+        <v>1089502</v>
       </c>
       <c r="C3">
-        <v>971610</v>
+        <v>978340</v>
       </c>
       <c r="D3">
-        <v>102557</v>
+        <v>111162</v>
       </c>
       <c r="E3">
-        <v>10.55536686530605</v>
+        <v>11.36230758223114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B4">
-        <v>1072011.5</v>
+        <v>1074167</v>
       </c>
       <c r="C4">
-        <v>956636</v>
+        <v>971610</v>
       </c>
       <c r="D4">
-        <v>115375.5</v>
+        <v>102557</v>
       </c>
       <c r="E4">
-        <v>12.06054340417881</v>
+        <v>10.55536686530605</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="B5">
-        <v>1022032</v>
+        <v>1072011.5</v>
       </c>
       <c r="C5">
-        <v>889630</v>
+        <v>956636</v>
       </c>
       <c r="D5">
-        <v>132402</v>
+        <v>115375.5</v>
       </c>
       <c r="E5">
-        <v>14.88281645178333</v>
+        <v>12.06054340417881</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="B6">
-        <v>983645</v>
+        <v>1022032</v>
       </c>
       <c r="C6">
-        <v>882037</v>
+        <v>889630</v>
       </c>
       <c r="D6">
-        <v>101608</v>
+        <v>132402</v>
       </c>
       <c r="E6">
-        <v>11.51969815325207</v>
+        <v>14.88281645178333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="B7">
-        <v>891250</v>
+        <v>983645</v>
       </c>
       <c r="C7">
-        <v>750000</v>
+        <v>882037</v>
       </c>
       <c r="D7">
-        <v>141250</v>
+        <v>101608</v>
       </c>
       <c r="E7">
-        <v>18.83333333333333</v>
+        <v>11.51969815325207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="B8">
-        <v>880000</v>
+        <v>891250</v>
       </c>
       <c r="C8">
-        <v>765050</v>
+        <v>750000</v>
       </c>
       <c r="D8">
-        <v>114950</v>
+        <v>141250</v>
       </c>
       <c r="E8">
-        <v>15.02516175413371</v>
+        <v>18.83333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Ollagüe</t>
         </is>
       </c>
       <c r="B9">
-        <v>879286</v>
+        <v>880000</v>
       </c>
       <c r="C9">
-        <v>771250</v>
+        <v>765050</v>
       </c>
       <c r="D9">
-        <v>108036</v>
+        <v>114950</v>
       </c>
       <c r="E9">
-        <v>14.00790923824959</v>
+        <v>15.02516175413371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>879286</v>
+      </c>
+      <c r="C10">
+        <v>771250</v>
+      </c>
+      <c r="D10">
+        <v>108036</v>
+      </c>
+      <c r="E10">
+        <v>14.00790923824959</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Sierra Gorda</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>800702</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>743079</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>57623</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>7.754626358704786</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_antofagasta.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,20 +588,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1074167</v>
+          <t>María Elena</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -610,48 +602,33 @@
           <t>Calama</t>
         </is>
       </c>
-      <c r="B3">
-        <v>1169074</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1072011.5</v>
+          <t>Tocopilla</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1022032</v>
+          <t>Antofagasta</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>880000</v>
+          <t>Mejillones</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>891250</v>
+          <t>Taltal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -660,28 +637,19 @@
           <t>Sierra Gorda</t>
         </is>
       </c>
-      <c r="B8">
-        <v>800702</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Taltal</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>879286</v>
+          <t>San Pedro de Atacama</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>983645</v>
+          <t>Ollagüe</t>
+        </is>
       </c>
     </row>
   </sheetData>
